--- a/Gear_Designer/gear.xlsx
+++ b/Gear_Designer/gear.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>1.2500</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>1.2500</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>38.0000</t>
+          <t>37.5000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.0000</t>
+          <t>18.7500</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>119.3805</t>
+          <t>117.8097</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2.0000</t>
+          <t>2.2500</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.2500</t>
         </is>
       </c>
     </row>
